--- a/source-data/Invited_Seminars.xlsx
+++ b/source-data/Invited_Seminars.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\CVs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsqua\Documents\GitHub\GithubRepo\robinerowland.github.io\source-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445F693-36C5-4C86-B51F-C3E2EE967E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38828E6-3416-4159-9814-8E7D54A01444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C33128FF-CFE0-4465-BB8F-F90A99D160D9}"/>
+    <workbookView xWindow="-23148" yWindow="2628" windowWidth="23256" windowHeight="12456" xr2:uid="{C33128FF-CFE0-4465-BB8F-F90A99D160D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Invited Seminars</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
       <rPr>
@@ -157,6 +154,32 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Invited Presentations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Introduction to Scientific Writing.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UniSC Ecological Society.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -164,7 +187,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="mmm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -226,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -237,8 +260,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,9 +283,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,7 +323,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -403,7 +429,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -545,7 +571,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -553,51 +579,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C00FB3-41B5-4CC0-8DB3-767D30C7FE83}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="58.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="4">
+        <v>46235</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46113</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>45931</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>45931</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="5" spans="1:2" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
+        <v>45839</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>45839</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="6" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
+        <v>45536</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>45536</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
